--- a/forms/trg/Formulir_TRG_biovax.xlsx
+++ b/forms/trg/Formulir_TRG_biovax.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B38)</f>
+        <f>COUNTA(Anggota!B5:B39)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F38)</f>
+        <f>COUNTA(Anggota!F5:F39)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Najdah Hidayah</t>
+          <t>Prof. dr. Muh. Nasrum Massi, Ph.D., Sp.MK(K).</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -926,7 +926,11 @@
           <t>Hasanuddin University, Indonesia</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer in the field of Clinical Microbiology with a subspecialty in Bacteriology, Expert in Tuberculosis (TB)</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -935,7 +939,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57226099460</t>
+          <t>8382737100</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -950,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>dr. Irda Handayani, Sp.PK, M.Kes</t>
+          <t>Najdah Hidayah</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -972,7 +976,7 @@
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57192910960</t>
+          <t>57226099460</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -987,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ahyar Ahmad, M.Si</t>
+          <t>dr. Irda Handayani, Sp.PK, M.Kes</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,7 +1013,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>7202040873</t>
+          <t>57192910960</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1024,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Rosana Agus, M.Si.</t>
+          <t>Prof. Dr. Ahyar Ahmad, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1046,7 +1050,7 @@
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57201349972</t>
+          <t>7202040873</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1061,17 +1065,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Professor Stephen Gordon</t>
+          <t>Prof. Dr. Rosana Agus, M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>University of Edinburgh, United Kingdom</t>
+          <t>Hasanuddin University, Indonesia</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1083,7 +1087,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>http://www.scopus.com/inward/authorDetails.url?authorID=7401829209&amp;partnerID=MN8TOARS</t>
+          <t>57201349972</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1098,27 +1102,31 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. rer.nat. Astutiati Nurhasanah</t>
+          <t>Professor Stephen Gordon</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Badan Riset dan Inovasi Nasional, Indonesia</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>University of Edinburgh, United Kingdom</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>http://www.scopus.com/inward/authorDetails.url?authorID=7401829209&amp;partnerID=MN8TOARS</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1131,31 +1139,27 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Thaigarajan Parumasivam</t>
+          <t>Dr. rer.nat. Astutiati Nurhasanah</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Universiti Sains Malaysia, Malaysia</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Badan Riset dan Inovasi Nasional, Indonesia</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>55745346400</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1168,17 +1172,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Handayani Halik</t>
+          <t>Dr. Thaigarajan Parumasivam</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Megarezky Makassar, Indonesia</t>
+          <t>Universiti Sains Malaysia, Malaysia</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1190,7 +1194,7 @@
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>42961330800</t>
+          <t>55745346400</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1205,17 +1209,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Professor Galina V. Mukamolova</t>
+          <t>Handayani Halik</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>University of Leicester, United Kingdom</t>
+          <t>Universitas Megarezky Makassar, Indonesia</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1225,7 +1229,11 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>42961330800</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1238,17 +1246,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Balqis Dinarty Jamaluddin</t>
+          <t>Professor Galina V. Mukamolova</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University, Indonesia</t>
+          <t>University of Leicester, United Kingdom</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1271,12 +1279,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ummi Chaera</t>
+          <t>Balqis Dinarty Jamaluddin</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1304,12 +1312,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Randi Rimpung</t>
+          <t>Ummi Chaera</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1337,12 +1345,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Eka Sry Wahyuni</t>
+          <t>Randi Rimpung</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1370,12 +1378,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Fadhilah Ananda Putri</t>
+          <t>Eka Sry Wahyuni</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1403,12 +1411,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Nadhila Idris</t>
+          <t>Fadhilah Ananda Putri</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1436,12 +1444,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Nurul Husna</t>
+          <t>Nadhila Idris</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1469,12 +1477,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Noer Zakiah Derajat Sam</t>
+          <t>Nurul Husna</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1502,12 +1510,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Muh Akbar Ardiputra, S.Si.</t>
+          <t>Noer Zakiah Derajat Sam</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1535,12 +1543,12 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Kresentia Anita Raniputri</t>
+          <t>Muh Akbar Ardiputra, S.Si.</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
@@ -1568,12 +1576,12 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Israwati</t>
+          <t>Kresentia Anita Raniputri</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
@@ -1601,12 +1609,12 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Benny Lumban Radja</t>
+          <t>Israwati</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
@@ -1634,12 +1642,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Ufi Dewintera</t>
+          <t>Benny Lumban Radja</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1647,11 +1655,7 @@
           <t>Hasanuddin University, Indonesia</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>BioVax Team</t>
-        </is>
-      </c>
+      <c r="E26" s="11" t="n"/>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
@@ -1669,10 +1673,26 @@
       <c r="A27" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="11" t="n"/>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Ufi Dewintera</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University, Indonesia</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>BioVax Team</t>
+        </is>
+      </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
@@ -1680,7 +1700,11 @@
       <c r="J27" s="12" t="n"/>
       <c r="K27" s="12" t="n"/>
       <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1869,15 +1893,32 @@
       <c r="L38" s="12" t="n"/>
       <c r="M38" s="12" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
